--- a/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
+++ b/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>39714.76</v>
+        <v>39510.7</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>143418.47</v>
+        <v>142633.04</v>
       </c>
     </row>
     <row r="4">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>142163.53</v>
+        <v>141384.98</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>53770.8</v>
+        <v>53702.36</v>
       </c>
     </row>
     <row r="6">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>210224.67</v>
+        <v>213853.47</v>
       </c>
     </row>
     <row r="7">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>238458.48</v>
+        <v>242574.63</v>
       </c>
     </row>
     <row r="8">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>77787.06</v>
+        <v>77666.49000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>24023.9</v>
+        <v>23986.66</v>
       </c>
     </row>
     <row r="10">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>41718.08</v>
+        <v>41933.53</v>
       </c>
     </row>
     <row r="11">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>41718.08</v>
+        <v>41933.53</v>
       </c>
     </row>
     <row r="12">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>49881.7</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="13">
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="14">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="15">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="16">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="17">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="18">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3290-353-CM25</t>
+          <t>1052231-117-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1052231-117-CM25</t>
+          <t>3290-353-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3276-37-CM25</t>
+          <t>2483-878-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1713,32 +1713,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t xml:space="preserve">AUTOMOTORA MELHUISH SPA </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.281.300-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>42607.59</v>
+        <v>36737.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3311-137-CM25</t>
+          <t>3276-37-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>42607.59</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3624-632-CM25</t>
+          <t>3311-137-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1830,37 +1830,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Cecor S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.010.151-6</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1870,13 +1870,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>56753.94</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>998-290-CM25</t>
+          <t>3624-632-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1891,51 +1891,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Janssen S.A.</t>
+          <t>Cecor S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>81.198.100-1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de los Lagos </t>
-        </is>
-      </c>
+          <t>76.010.151-6</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>114363.85</v>
+        <v>56189.26</v>
       </c>
     </row>
     <row r="25">
@@ -1996,13 +1992,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>66277.28999999999</v>
+        <v>66039.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1001-280-SE25</t>
+          <t>998-290-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2017,12 +2013,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2037,22 +2033,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EQUIPOS Y CAMIONES SPA</t>
+          <t>Janssen S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.517.323-8</t>
+          <t>81.198.100-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de los Lagos </t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,13 +2057,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>154308.04</v>
+        <v>113953.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1001-279-CM25</t>
+          <t>1001-275-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2107,12 +2103,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2126,13 +2122,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>49950.28</v>
+        <v>146159.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1001-275-CM25</t>
+          <t>1001-277-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2172,17 +2168,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Biobío </t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2191,13 +2187,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>146476.45</v>
+        <v>245677.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1001-277-CM25</t>
+          <t>1001-279-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2237,17 +2233,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2256,13 +2252,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>246210.53</v>
+        <v>49842.18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3326-621-CM25</t>
+          <t>1001-280-SE25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2277,53 +2273,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>EQUIPOS Y CAMIONES SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>77.517.323-8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>59359.52</v>
+        <v>153974.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1001-295-CM25</t>
+          <t>3326-621-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2343,32 +2343,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2378,13 +2378,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>26407.84</v>
+        <v>58856.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3326-624-CM25</t>
+          <t>1001-295-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2399,37 +2399,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>20596.44</v>
+        <v>26184.15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2366-4462-CM25</t>
+          <t>3326-624-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2500,13 +2500,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>73205.75</v>
+        <v>20579.89</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2585-4705-CM25</t>
+          <t>2366-4461-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2561,13 +2561,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>21497.76</v>
+        <v>69219.13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2366-4461-CM25</t>
+          <t>2585-4705-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>68954.47</v>
+        <v>21580.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5240-296-CM25</t>
+          <t>2366-4462-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2653,47 +2653,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>290657.08</v>
+        <v>73486.73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>979-2135-CM25</t>
+          <t>5240-296-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2713,17 +2709,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2733,12 +2729,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2752,13 +2748,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>580067.77</v>
+        <v>291974.24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3326-606-CM25</t>
+          <t>979-2135-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2773,22 +2769,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2798,12 +2794,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2817,13 +2813,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>279545.37</v>
+        <v>582696.4300000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1596-387-CM25</t>
+          <t>3326-606-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2838,7 +2834,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2848,27 +2844,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2882,13 +2878,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>109847.59</v>
+        <v>279903.74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2560-127-CM25</t>
+          <t>2483-975-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2903,7 +2899,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2913,12 +2909,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2928,32 +2924,28 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>94856.52</v>
+        <v>37653.91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>624-379-CM25</t>
+          <t>1596-387-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2963,47 +2955,47 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3012,13 +3004,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>387809.16</v>
+        <v>110786.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2560-141-CM25</t>
+          <t>624-379-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3033,7 +3025,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3043,32 +3035,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Región del Ñuble</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3077,7 +3069,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>124884.17</v>
+        <v>382886.76</v>
       </c>
     </row>
     <row r="43">
@@ -3138,7 +3130,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>35319.24</v>
+        <v>35097.92</v>
       </c>
     </row>
     <row r="44">
@@ -3199,7 +3191,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>46936.21</v>
+        <v>48077.59</v>
       </c>
     </row>
     <row r="45">
@@ -3260,7 +3252,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>36638.34</v>
+        <v>37727.35</v>
       </c>
     </row>
     <row r="46">
@@ -3321,7 +3313,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>68209.44</v>
+        <v>68816.96000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3382,7 +3374,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>29547.92</v>
+        <v>29387.01</v>
       </c>
     </row>
     <row r="48">
@@ -3447,7 +3439,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>220060.09</v>
+        <v>218722.92</v>
       </c>
     </row>
     <row r="49">
@@ -3512,7 +3504,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>124329.61</v>
+        <v>123574.14</v>
       </c>
     </row>
     <row r="50">
@@ -3577,7 +3569,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>155676.55</v>
+        <v>154730.6</v>
       </c>
     </row>
     <row r="51">
@@ -3642,7 +3634,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>126768.29</v>
+        <v>123430.06</v>
       </c>
     </row>
     <row r="52">
@@ -3703,7 +3695,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>30285.23</v>
+        <v>30629.64</v>
       </c>
     </row>
     <row r="53">
@@ -3764,13 +3756,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>36985.96</v>
+        <v>36894.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3624-312-CM26</t>
+          <t>3624-311-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3810,12 +3802,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3825,13 +3817,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>72690.97</v>
+        <v>26694.05</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3624-311-CM26</t>
+          <t>3624-312-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3871,12 +3863,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3886,7 +3878,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>27078.35</v>
+        <v>71659.32000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3947,7 +3939,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>32364.52</v>
+        <v>32163.87</v>
       </c>
     </row>
     <row r="57">
@@ -4008,7 +4000,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>70315.81</v>
+        <v>70635.16</v>
       </c>
     </row>
     <row r="58">
@@ -4069,7 +4061,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>28194.2</v>
+        <v>28388.86</v>
       </c>
     </row>
     <row r="59">
@@ -4130,13 +4122,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>61996.23</v>
+        <v>62187.89</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2345-260-CM26</t>
+          <t>5042-25-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4146,12 +4138,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4161,27 +4153,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4191,13 +4183,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>27885.14</v>
+        <v>22670.48</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2345-261-CM26</t>
+          <t>3624-359-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4207,12 +4199,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4222,27 +4214,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4252,13 +4244,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>603.08</v>
+        <v>18595.48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5042-25-CM26</t>
+          <t>624-133-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4273,7 +4265,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4283,27 +4275,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4313,13 +4305,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>22445.72</v>
+        <v>43688.38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3624-359-CM26</t>
+          <t>5240-180-SE26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4334,53 +4326,57 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>18411.12</v>
+        <v>121520.79</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>624-133-CM26</t>
+          <t>2483-461-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4395,7 +4391,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4405,27 +4401,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4435,13 +4431,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>43518.97</v>
+        <v>15908.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5240-180-SE26</t>
+          <t>3820-637-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4456,7 +4452,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4466,47 +4462,43 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>120712.8</v>
+        <v>17210.12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3820-637-CM26</t>
+          <t>3820-638-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4561,13 +4553,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>17244.69</v>
+        <v>397.75</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3820-638-CM26</t>
+          <t>5240-169-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4582,37 +4574,37 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4622,13 +4614,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>398.55</v>
+        <v>166290.37</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5240-169-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4653,27 +4645,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4683,13 +4675,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>169017.9</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>1596-186-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4744,13 +4736,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>41999.21</v>
+        <v>1340.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>1782-12-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4765,7 +4757,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4775,43 +4767,47 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Gobierno Regional de Antofagasta</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1362.08</v>
+        <v>654540.41</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1782-12-CM26</t>
+          <t>3326-455-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4821,56 +4817,239 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.938.500-4</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>29282.78</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3326-457-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>72.224.100-2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Gobierno Regional de Antofagasta</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.938.500-4</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>650188.38</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>43132.89</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1596-199-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>113982.42</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2483-560-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>69.071.300-4</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>216182.5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
+++ b/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M199"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3326-20-CM25</t>
+          <t>29-16-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>KIA CHILE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>79.567.420-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>33236.46</v>
+        <v>39244.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3326-32-CM25</t>
+          <t>3326-20-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>15952.32</v>
+        <v>33236.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3326-34-CM25</t>
+          <t>3326-32-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>53786.51</v>
+        <v>15952.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3326-40-CM25</t>
+          <t>3326-34-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>21163.86</v>
+        <v>53786.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3326-41-CM25</t>
+          <t>3326-40-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>33187.7</v>
+        <v>21163.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3326-42-CM25</t>
+          <t>3326-41-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>25005.21</v>
+        <v>33187.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3326-54-CM25</t>
+          <t>3326-42-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>20396.22</v>
+        <v>25005.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1067526-35-CM25</t>
+          <t>3326-54-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>70508.50999999999</v>
+        <v>20396.22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1067526-36-CM25</t>
+          <t>3326-69-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,27 +1088,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DERCOMAQ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.545.450-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>34543.78</v>
+        <v>28911.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3326-69-CM25</t>
+          <t>1018-47-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>28911.07</v>
+        <v>24951.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1018-47-CM25</t>
+          <t>4374-1-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,53 +1200,57 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>24951.73</v>
+        <v>106344.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4374-1-CM25</t>
+          <t>4229-16-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,47 +1275,43 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>106344.99</v>
+        <v>20665.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4229-16-CM25</t>
+          <t>3326-90-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>20665.57</v>
+        <v>16699.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3326-90-CM25</t>
+          <t>796297-29-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,27 +1397,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>16699.2</v>
+        <v>44571.26</v>
       </c>
     </row>
     <row r="17">
@@ -2409,7 +2409,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>539119-3510-CM25</t>
+          <t>29-146-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>31850.29</v>
+        <v>49898.67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1094-3-CM25</t>
+          <t>29-147-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,37 +2485,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>26458.93</v>
+        <v>22495.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5190-186-CM25</t>
+          <t>1018-80-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,28 +2571,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>27121.28</v>
+        <v>113226.34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>557970-21-CM25</t>
+          <t>3326-179-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2612,32 +2616,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2651,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>27121.28</v>
+        <v>20551.71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1018-80-CM25</t>
+          <t>539119-3510-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2673,52 +2677,48 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>113226.34</v>
+        <v>31850.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3326-179-CM25</t>
+          <t>1094-3-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2738,32 +2738,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2773,13 +2773,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>20551.71</v>
+        <v>26458.93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5240-93-CM25</t>
+          <t>5190-186-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2819,32 +2819,28 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>266842.13</v>
+        <v>27121.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1096-52-CM25</t>
+          <t>557970-21-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2854,17 +2850,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2879,17 +2875,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>KOMATSU CHILE S.A.- CASA MATRIZ</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.843.130-7</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2899,13 +2895,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>370810.97</v>
+        <v>27121.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5240-92-CM25</t>
+          <t>1096-52-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2920,7 +2916,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2930,47 +2926,43 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>KOMATSU CHILE S.A.- CASA MATRIZ</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.843.130-7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>25022.09</v>
+        <v>370810.97</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3326-201-CM25</t>
+          <t>5240-93-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2985,7 +2977,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3010,28 +3002,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>24484.07</v>
+        <v>266842.13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1063796-29-CM25</t>
+          <t>5240-92-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3046,7 +3042,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3056,43 +3052,47 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.150.400-k</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>10189.2</v>
+        <v>25022.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3595-188-CM25</t>
+          <t>3326-201-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3117,47 +3117,43 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>82034.28</v>
+        <v>24484.07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3326-209-CM25</t>
+          <t>3595-188-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3172,7 +3168,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3182,43 +3178,47 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>22716.93</v>
+        <v>82034.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3474-390-CM25</t>
+          <t>3326-209-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>35603.63</v>
+        <v>22716.93</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3474-410-CM25</t>
+          <t>3474-390-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>48335.27</v>
+        <v>35603.63</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3326-236-CM25</t>
+          <t>3474-410-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>28453.69</v>
+        <v>48335.27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1271-23-CM25</t>
+          <t>3326-236-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3426,27 +3426,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3456,13 +3456,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>26380.6</v>
+        <v>28453.69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1268-33-CM25</t>
+          <t>1271-23-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>26093.86</v>
+        <v>26380.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3326-240-CM25</t>
+          <t>1268-33-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3548,27 +3548,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>28534</v>
+        <v>26093.86</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5240-112-CM25</t>
+          <t>3326-240-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3624,32 +3624,28 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>298849.7</v>
+        <v>28534</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>976-171-CM25</t>
+          <t>5240-112-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3664,7 +3660,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3674,12 +3670,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3689,28 +3685,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>27383.7</v>
+        <v>298849.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5240-98-CM25</t>
+          <t>976-171-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3750,32 +3750,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>60218.1</v>
+        <v>27383.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>975-120-CM25</t>
+          <t>5240-98-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3795,17 +3791,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3815,17 +3811,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3834,13 +3830,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>210423.71</v>
+        <v>60218.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3326-259-CM25</t>
+          <t>975-120-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3855,22 +3851,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3880,28 +3876,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>19259.23</v>
+        <v>210423.71</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3326-263-CM25</t>
+          <t>3326-259-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3916,12 +3916,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3956,13 +3956,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>49998.52</v>
+        <v>19259.23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4374-58-CM25</t>
+          <t>3326-263-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3977,57 +3977,53 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>474892.33</v>
+        <v>49998.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3326-277-CM25</t>
+          <t>4374-58-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4037,12 +4033,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4052,43 +4048,47 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>33736.15</v>
+        <v>474892.33</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1596-160-CM25</t>
+          <t>3326-277-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4113,47 +4113,43 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>213461.61</v>
+        <v>33736.15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5240-165-CM25</t>
+          <t>1596-160-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4168,7 +4164,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4178,43 +4174,47 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>94924.60000000001</v>
+        <v>213461.61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3595-281-CM25</t>
+          <t>5240-165-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4239,27 +4239,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>35676.71</v>
+        <v>94924.60000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3326-296-CM25</t>
+          <t>3595-281-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4300,27 +4300,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4330,13 +4330,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>28411.88</v>
+        <v>35676.71</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1044-49-CM25</t>
+          <t>3326-296-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4351,22 +4351,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>DERCOMAQ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.545.450-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4391,13 +4391,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>66160.02</v>
+        <v>28411.88</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3326-298-CM25</t>
+          <t>1044-49-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4417,17 +4417,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4452,13 +4452,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>27750.29</v>
+        <v>66160.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4374-63-CM25</t>
+          <t>3326-298-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4483,47 +4483,43 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>75561.98</v>
+        <v>27750.29</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3595-308-CM25</t>
+          <t>4374-63-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4538,7 +4534,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4548,43 +4544,47 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>44302.74</v>
+        <v>75561.98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2369-37-CM25</t>
+          <t>3595-308-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4609,17 +4609,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4632,24 +4632,20 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>364772.75</v>
+        <v>44302.74</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3326-318-CM25</t>
+          <t>2369-37-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4664,7 +4660,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4674,43 +4670,47 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>20521.92</v>
+        <v>364772.75</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4988-33-CM25</t>
+          <t>3326-318-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4735,27 +4735,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Cecor S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.010.151-6</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>43838.88</v>
+        <v>20521.92</v>
       </c>
     </row>
     <row r="71">
@@ -4958,7 +4958,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4988-39-CM25</t>
+          <t>3326-357-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4983,47 +4983,43 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>230449.24</v>
+        <v>27954.44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3326-357-CM25</t>
+          <t>1051425-97-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5038,7 +5034,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5048,27 +5044,27 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5078,13 +5074,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>27954.44</v>
+        <v>35723.62</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1051425-97-CM25</t>
+          <t>1455288-29-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5099,7 +5095,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5109,27 +5105,27 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5139,13 +5135,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>35723.62</v>
+        <v>23929.56</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3326-374-CM25</t>
+          <t>2974-514-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5170,12 +5166,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5185,12 +5181,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5200,13 +5196,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>27881.27</v>
+        <v>24152.48</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1596-208-CM25</t>
+          <t>3326-374-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5221,7 +5217,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5231,17 +5227,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5254,24 +5250,20 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>133329.6</v>
+        <v>27881.27</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>609-329-CM25</t>
+          <t>1596-208-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5286,7 +5278,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5296,32 +5288,32 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5330,7 +5322,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>404994.09</v>
+        <v>133329.6</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5393,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3326-373-CM25</t>
+          <t>609-329-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5416,7 +5408,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5426,12 +5418,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5441,28 +5433,32 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>24148.54</v>
+        <v>404994.09</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2585-4029-CM25</t>
+          <t>3326-373-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5477,7 +5473,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5487,27 +5483,27 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5517,13 +5513,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>34510.01</v>
+        <v>24148.54</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1596-206-CM25</t>
+          <t>2585-4029-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5548,47 +5544,43 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>149130.92</v>
+        <v>34510.01</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3326-368-CM25</t>
+          <t>1596-206-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5603,7 +5595,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5613,43 +5605,47 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>27179.81</v>
+        <v>149130.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1063487-18-CM25</t>
+          <t>3326-368-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5664,37 +5660,37 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5704,13 +5700,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>26136.66</v>
+        <v>27179.81</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3326-399-CM25</t>
+          <t>1063487-18-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5720,42 +5716,42 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5765,13 +5761,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>66891.19</v>
+        <v>26136.66</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1020-329-CM25</t>
+          <t>3326-399-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5786,22 +5782,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5811,12 +5807,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5826,13 +5822,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>28349.18</v>
+        <v>66891.19</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1002-409-CM25</t>
+          <t>1020-329-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5847,7 +5843,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5867,17 +5863,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5887,13 +5883,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>34923.02</v>
+        <v>28349.18</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1020-327-CM25</t>
+          <t>1002-409-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5908,7 +5904,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5928,31 +5924,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>80696.36</v>
+        <v>34923.02</v>
       </c>
     </row>
     <row r="90">
@@ -6019,7 +6011,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>979-1634-CM25</t>
+          <t>1020-327-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6034,12 +6026,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6059,28 +6051,32 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>48009.23</v>
+        <v>80696.36</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>998-218-CM25</t>
+          <t>998-219-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6120,12 +6116,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6135,13 +6131,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>50934.76</v>
+        <v>34793.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>998-219-CM25</t>
+          <t>998-218-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6181,12 +6177,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6196,13 +6192,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>34793.4</v>
+        <v>50934.76</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1051425-105-CM25</t>
+          <t>979-1634-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6237,17 +6233,17 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Cecor S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.010.151-6</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6257,13 +6253,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>42740.31</v>
+        <v>48009.23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3326-450-CM25</t>
+          <t>1051425-105-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6278,7 +6274,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6288,27 +6284,27 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Cecor S.A.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>76.010.151-6</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6318,13 +6314,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>25615.13</v>
+        <v>42740.31</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1284411-22-CM25</t>
+          <t>3326-450-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6334,27 +6330,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6364,32 +6360,28 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>114075.35</v>
+        <v>25615.13</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>539119-7588-CM25</t>
+          <t>1284411-22-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6409,17 +6401,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6429,28 +6421,32 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>67461.47</v>
+        <v>114075.35</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2216-637-CM25</t>
+          <t>539119-7588-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6470,17 +6466,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>MOP Dirección General de Concesiones</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6490,12 +6486,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6505,7 +6501,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>26666.6</v>
+        <v>67461.47</v>
       </c>
     </row>
     <row r="99">
@@ -7304,7 +7300,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1002-452-CM25</t>
+          <t>1002-453-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7344,12 +7340,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7363,13 +7359,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>149680.45</v>
+        <v>154173.32</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1002-453-CM25</t>
+          <t>1002-452-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7409,12 +7405,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7428,7 +7424,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>154173.32</v>
+        <v>149680.45</v>
       </c>
     </row>
     <row r="114">
@@ -7647,7 +7643,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7769,7 +7765,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7830,7 +7826,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7891,7 +7887,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7952,7 +7948,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8088,7 +8084,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8204,7 +8200,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8265,7 +8261,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8326,7 +8322,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8387,7 +8383,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8448,7 +8444,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8479,7 +8475,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3326-552-CM25</t>
+          <t>3326-551-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8519,17 +8515,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8538,13 +8534,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>242574.63</v>
+        <v>213853.47</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4232-160-CM25</t>
+          <t>3326-552-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8569,22 +8565,22 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8592,20 +8588,24 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>25371.37</v>
+        <v>242574.63</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3326-551-CM25</t>
+          <t>4232-160-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8640,31 +8640,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>213853.47</v>
+        <v>25371.37</v>
       </c>
     </row>
     <row r="134">
@@ -8700,7 +8696,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8761,7 +8757,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8822,7 +8818,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8853,7 +8849,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4230-173-CM25</t>
+          <t>539119-10421-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8878,27 +8874,27 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8908,13 +8904,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>24888.81</v>
+        <v>17279.98</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>539119-10421-CM25</t>
+          <t>4230-173-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8939,27 +8935,27 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8969,13 +8965,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>17279.98</v>
+        <v>24888.81</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1080164-33-CM25</t>
+          <t>4232-159-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9000,22 +8996,22 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9036,7 +9032,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1080164-35-CM25</t>
+          <t>1080164-33-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9066,7 +9062,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9076,7 +9072,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9091,13 +9087,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>24896.61</v>
+        <v>29008.6</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4232-159-CM25</t>
+          <t>1080164-35-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9122,22 +9118,22 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9152,7 +9148,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>29008.6</v>
+        <v>24896.61</v>
       </c>
     </row>
     <row r="142">
@@ -9188,7 +9184,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Car</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9259,7 +9255,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9467,7 +9463,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3326-597-CM25</t>
+          <t>29-589-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9492,12 +9488,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9507,12 +9503,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9522,7 +9518,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>50233.74</v>
+        <v>49083.79</v>
       </c>
     </row>
     <row r="148">
@@ -9558,7 +9554,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9568,7 +9564,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9589,7 +9585,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5592-3352-CM25</t>
+          <t>796305-80-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9599,32 +9595,32 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9644,13 +9640,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>42056.86</v>
+        <v>17662.63</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3289-226-CM25</t>
+          <t>3326-597-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9660,12 +9656,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9675,27 +9671,27 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9705,13 +9701,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>42056.86</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3319-249-CM25</t>
+          <t>2974-641-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9721,12 +9717,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9736,17 +9732,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9766,7 +9762,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>42056.86</v>
+        <v>46279.36</v>
       </c>
     </row>
     <row r="152">
@@ -10077,7 +10073,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3276-37-CM25</t>
+          <t>3319-249-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10092,7 +10088,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10112,7 +10108,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10132,13 +10128,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>42066.38</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3311-137-CM25</t>
+          <t>3289-226-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10153,7 +10149,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10173,7 +10169,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10193,13 +10189,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>42066.38</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>998-290-CM25</t>
+          <t>5592-3352-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10214,7 +10210,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10224,47 +10220,43 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Janssen S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>81.198.100-1</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>113953.77</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3326-610-CM25</t>
+          <t>3311-137-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10279,7 +10271,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10289,27 +10281,27 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10319,13 +10311,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>66039.63</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1001-275-CM25</t>
+          <t>3276-37-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10340,57 +10332,53 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>146159.45</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1001-277-CM25</t>
+          <t>3326-610-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10405,57 +10393,53 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>245677.7</v>
+        <v>66039.63</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1001-279-CM25</t>
+          <t>998-290-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10470,12 +10454,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10490,22 +10474,22 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Janssen S.A.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>81.198.100-1</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10514,13 +10498,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>49842.18</v>
+        <v>113953.77</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1001-280-SE25</t>
+          <t>1001-275-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10560,12 +10544,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>EQUIPOS Y CAMIONES SPA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>77.517.323-8</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -10579,13 +10563,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>153974.09</v>
+        <v>146159.45</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1001-295-CM25</t>
+          <t>1001-277-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10600,7 +10584,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10625,28 +10609,32 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>26184.15</v>
+        <v>245677.7</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3326-621-CM25</t>
+          <t>1001-279-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10661,53 +10649,57 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>58856.7</v>
+        <v>49842.18</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3326-624-CM25</t>
+          <t>1001-280-SE25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10722,53 +10714,57 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>EQUIPOS Y CAMIONES SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>77.517.323-8</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>20579.89</v>
+        <v>153974.09</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2585-4705-CM25</t>
+          <t>3326-621-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10783,7 +10779,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10793,27 +10789,27 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10823,13 +10819,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>21580.27</v>
+        <v>58856.7</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2366-4461-CM25</t>
+          <t>1001-295-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10844,37 +10840,37 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10884,13 +10880,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>69219.13</v>
+        <v>26184.15</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2366-4462-CM25</t>
+          <t>3326-624-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10905,7 +10901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10915,27 +10911,27 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10945,13 +10941,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>73486.73</v>
+        <v>20579.89</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>979-2135-CM25</t>
+          <t>2366-4462-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10966,57 +10962,53 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>582696.4300000001</v>
+        <v>73486.73</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5240-296-CM25</t>
+          <t>2585-4705-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11031,7 +11023,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -11041,47 +11033,43 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>291974.24</v>
+        <v>21580.27</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3326-606-CM25</t>
+          <t>2366-4461-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11096,7 +11084,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11106,47 +11094,43 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>279903.74</v>
+        <v>69219.13</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1596-387-CM25</t>
+          <t>979-2135-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11161,37 +11145,37 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -11205,13 +11189,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>110786.33</v>
+        <v>582696.4300000001</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3326-39-CM26</t>
+          <t>5240-296-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11221,12 +11205,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11251,28 +11235,32 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>48077.59</v>
+        <v>291974.24</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3326-47-CM26</t>
+          <t>3326-606-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11282,12 +11270,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11312,28 +11300,32 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>37727.35</v>
+        <v>279903.74</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2369-117-CM25</t>
+          <t>794947-149-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11343,12 +11335,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11358,17 +11350,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11381,24 +11373,20 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>218722.92</v>
+        <v>33093.64</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1596-40-CM26</t>
+          <t>1596-387-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11408,12 +11396,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11438,17 +11426,17 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11457,13 +11445,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>123574.14</v>
+        <v>110786.33</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1596-42-CM26</t>
+          <t>3326-39-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11473,12 +11461,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11488,47 +11476,43 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>154730.6</v>
+        <v>48077.59</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4988-6-CM26</t>
+          <t>3326-47-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11538,62 +11522,58 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Guillermo Morales Ltda</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.564.810-0</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>104460.72</v>
+        <v>37727.35</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5190-115-CM26</t>
+          <t>1596-42-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11603,12 +11583,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11618,119 +11598,127 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>23948.71</v>
+        <v>154730.6</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3595-140-CM26</t>
+          <t>2369-117-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>75622.14</v>
+        <v>218722.92</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>539119-1130-CM26</t>
+          <t>1596-40-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11740,58 +11728,62 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>42400.66</v>
+        <v>123574.14</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1080936-82-CM26</t>
+          <t>29-1421-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11801,12 +11793,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>60.506.012-9</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondos Extrapresupuestarios Escipol </t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11816,12 +11808,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11831,58 +11823,58 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>74050.67999999999</v>
+        <v>50773.11</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1596-123-CM26</t>
+          <t>5190-115-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11892,28 +11884,28 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>36894.63</v>
+        <v>23948.71</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3595-236-CM26</t>
+          <t>3595-140-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11938,12 +11930,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11953,13 +11945,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>38997.21</v>
+        <v>75622.14</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1269-43-CM26</t>
+          <t>539119-1130-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11969,42 +11961,42 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -12014,13 +12006,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>28388.86</v>
+        <v>42400.66</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2585-483-CM26</t>
+          <t>796297-45-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12030,12 +12022,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -12045,17 +12037,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12075,13 +12067,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>62187.89</v>
+        <v>39644.24</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5042-25-CM26</t>
+          <t>1080936-82-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12091,42 +12083,42 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.506.012-9</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -12136,13 +12128,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>22670.48</v>
+        <v>74050.67999999999</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5240-180-SE26</t>
+          <t>29-1644-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12152,12 +12144,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12167,12 +12159,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12182,32 +12174,28 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>121520.79</v>
+        <v>57146.37</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5240-169-CM26</t>
+          <t>1596-123-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12217,12 +12205,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12232,27 +12220,27 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12262,13 +12250,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>166290.37</v>
+        <v>36894.63</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>3595-236-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12278,42 +12266,42 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12323,13 +12311,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>41321.44</v>
+        <v>38997.21</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>1269-43-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12339,12 +12327,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12354,27 +12342,27 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12384,13 +12372,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1340.1</v>
+        <v>28388.86</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1782-12-CM26</t>
+          <t>2585-483-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12400,62 +12388,58 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>654540.41</v>
+        <v>62187.89</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2416-201-CM26</t>
+          <t>5042-25-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12465,42 +12449,42 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12510,13 +12494,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>42840</v>
+        <v>22670.48</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4374-44-CM26</t>
+          <t>5240-180-SE26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12526,58 +12510,62 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>25010.09</v>
+        <v>121520.79</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3326-455-CM26</t>
+          <t>5240-169-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12587,12 +12575,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12617,12 +12605,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12632,13 +12620,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>29282.78</v>
+        <v>166290.37</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1596-199-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12648,12 +12636,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12678,32 +12666,28 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>113982.42</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3326-457-CM26</t>
+          <t>1596-186-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12713,12 +12697,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12728,27 +12712,27 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12758,7 +12742,633 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
+        <v>1340.1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1782-12-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>72.224.100-2</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>654540.41</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>4374-44-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>72.240.400-9</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>25010.09</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1596-199-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>113982.42</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>3326-455-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>61.938.500-4</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>29282.78</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>3326-457-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>61.938.500-4</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
         <v>43132.89</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2585-931-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>38112.64</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>5240-192-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>61.938.500-4</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>61547.18</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>29-1907-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>61.103.035-5</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>58176.41</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>29-1925-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>61.103.035-5</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>74255.63</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1596-228-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>122392.49</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
+++ b/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M209"/>
+  <dimension ref="A1:M210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1185,7 +1225,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4374-1-CM25</t>
+          <t>4229-16-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,32 +1250,32 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1244,13 +1284,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>106344.99</v>
+        <v>20665.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4229-16-CM25</t>
+          <t>4374-1-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1275,37 +1315,41 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>20665.57</v>
+        <v>106344.99</v>
       </c>
     </row>
     <row r="15">
@@ -1359,7 +1403,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1468,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1655,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1720,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1677,7 +1737,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1207-1-CM25</t>
+          <t>937-2-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1712,7 +1772,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1725,7 +1785,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1738,7 +1802,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>937-2-CM25</t>
+          <t>1207-1-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1773,7 +1837,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1786,7 +1850,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1915,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1980,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2045,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2110,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2236,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2301,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2366,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2492,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2409,7 +2509,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29-146-CM25</t>
+          <t>29-147-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2449,28 +2549,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>49898.67</v>
+        <v>22495.04</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>29-147-CM25</t>
+          <t>29-146-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2510,28 +2614,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22495.04</v>
+        <v>49898.67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1018-80-CM25</t>
+          <t>3326-179-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2551,17 +2659,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,17 +2679,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2590,13 +2698,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>113226.34</v>
+        <v>20551.71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3326-179-CM25</t>
+          <t>539119-3510-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2621,7 +2729,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2631,33 +2739,37 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>20551.71</v>
+        <v>31850.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>539119-3510-CM25</t>
+          <t>1094-3-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2677,17 +2789,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2705,20 +2817,24 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>31850.29</v>
+        <v>26458.93</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1094-3-CM25</t>
+          <t>5190-186-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2738,48 +2854,52 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>26458.93</v>
+        <v>27121.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5190-186-CM25</t>
+          <t>557970-21-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2799,22 +2919,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2827,7 +2947,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2840,7 +2964,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>557970-21-CM25</t>
+          <t>1018-80-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2875,33 +2999,37 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>27121.28</v>
+        <v>113226.34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1096-52-CM25</t>
+          <t>5240-93-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2926,43 +3054,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>KOMATSU CHILE S.A.- CASA MATRIZ</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.843.130-7</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>370810.97</v>
+        <v>266842.13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5240-93-CM25</t>
+          <t>1096-52-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2987,32 +3119,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>KOMATSU CHILE S.A.- CASA MATRIZ</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.843.130-7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3021,7 +3153,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>266842.13</v>
+        <v>370810.97</v>
       </c>
     </row>
     <row r="43">
@@ -3140,7 +3272,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3266,7 +3402,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3327,7 +3467,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3388,7 +3532,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3449,7 +3597,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3510,7 +3662,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3571,7 +3727,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3632,7 +3792,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3758,7 +3922,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3771,7 +3939,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5240-98-CM25</t>
+          <t>975-120-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3791,17 +3959,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3811,17 +3979,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3830,13 +3998,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>60218.1</v>
+        <v>210423.71</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>975-120-CM25</t>
+          <t>5240-98-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3856,17 +4024,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3876,17 +4044,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3895,7 +4063,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>210423.71</v>
+        <v>60218.1</v>
       </c>
     </row>
     <row r="57">
@@ -3949,7 +4117,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4010,7 +4182,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4136,7 +4312,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4323,7 +4503,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4384,7 +4568,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4445,7 +4633,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4506,7 +4698,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4632,7 +4828,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4758,7 +4958,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4884,7 +5088,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4945,7 +5153,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5006,7 +5218,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5128,7 +5344,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5189,7 +5409,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5250,7 +5474,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5328,7 +5556,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>609-337-CM25</t>
+          <t>609-329-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5368,17 +5596,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5387,13 +5615,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>135478.99</v>
+        <v>404994.09</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>609-329-CM25</t>
+          <t>609-337-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5433,17 +5661,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5452,7 +5680,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>404994.09</v>
+        <v>135478.99</v>
       </c>
     </row>
     <row r="82">
@@ -5506,7 +5734,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5567,7 +5799,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5693,7 +5929,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5754,7 +5994,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5815,7 +6059,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5876,7 +6124,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5937,7 +6189,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6124,7 +6380,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6185,7 +6445,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6246,7 +6510,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6368,7 +6636,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6494,7 +6766,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6677,7 +6953,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6690,7 +6970,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3326-489-CM25</t>
+          <t>3326-495-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6730,28 +7010,32 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>20419.51</v>
+        <v>44016.94</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3326-495-CM25</t>
+          <t>3326-489-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6791,22 +7075,26 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>44016.94</v>
+        <v>20419.51</v>
       </c>
     </row>
     <row r="104">
@@ -6860,7 +7148,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6982,7 +7274,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7043,7 +7339,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7104,7 +7404,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7165,7 +7469,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7226,7 +7534,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7287,7 +7599,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7300,7 +7616,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1002-453-CM25</t>
+          <t>1002-452-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7340,12 +7656,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7359,13 +7675,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>154173.32</v>
+        <v>149680.45</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1002-452-CM25</t>
+          <t>1002-453-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7405,12 +7721,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7424,13 +7740,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>149680.45</v>
+        <v>154173.32</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3434-115-CM25</t>
+          <t>3326-535-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7455,7 +7771,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7465,33 +7781,37 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>24601.88</v>
+        <v>30610.16</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3326-535-CM25</t>
+          <t>3434-115-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7516,7 +7836,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7526,27 +7846,31 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>30610.16</v>
+        <v>24601.88</v>
       </c>
     </row>
     <row r="116">
@@ -7600,7 +7924,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7661,7 +7989,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7674,7 +8006,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1095-90-CM25</t>
+          <t>4230-160-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7694,48 +8026,52 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>39510.7</v>
+        <v>25413.54</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4230-160-CM25</t>
+          <t>1095-90-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7755,42 +8091,46 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>25413.54</v>
+        <v>39510.7</v>
       </c>
     </row>
     <row r="120">
@@ -7844,7 +8184,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7905,7 +8249,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7966,7 +8314,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7979,7 +8331,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1340-9047-CM25</t>
+          <t>1340-9046-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8019,12 +8371,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8038,13 +8390,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>141384.98</v>
+        <v>142633.04</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1340-9046-CM25</t>
+          <t>1340-9047-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8084,12 +8436,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8103,7 +8455,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>142633.04</v>
+        <v>141384.98</v>
       </c>
     </row>
     <row r="125">
@@ -8157,7 +8509,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8218,7 +8574,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8279,7 +8639,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8340,7 +8704,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8401,7 +8769,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8462,7 +8834,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8540,7 +8916,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3326-552-CM25</t>
+          <t>4232-160-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8565,7 +8941,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8575,7 +8951,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8599,13 +8975,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>242574.63</v>
+        <v>25371.37</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4232-160-CM25</t>
+          <t>3326-552-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8630,7 +9006,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8640,7 +9016,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8653,14 +9029,18 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>25371.37</v>
+        <v>242574.63</v>
       </c>
     </row>
     <row r="134">
@@ -8714,7 +9094,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8775,7 +9159,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8836,7 +9224,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8849,7 +9241,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>539119-10421-CM25</t>
+          <t>4230-173-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8874,7 +9266,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8884,33 +9276,37 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>17279.98</v>
+        <v>24888.81</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4230-173-CM25</t>
+          <t>539119-10421-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8935,7 +9331,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8945,33 +9341,37 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>24888.81</v>
+        <v>17279.98</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4232-159-CM25</t>
+          <t>1080164-35-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8996,7 +9396,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -9006,7 +9406,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9019,20 +9419,24 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>29008.6</v>
+        <v>24896.61</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1080164-33-CM25</t>
+          <t>4232-159-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9057,7 +9461,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -9067,7 +9471,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9080,7 +9484,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9093,7 +9501,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1080164-35-CM25</t>
+          <t>1080164-33-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9141,14 +9549,18 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>24896.61</v>
+        <v>29008.6</v>
       </c>
     </row>
     <row r="142">
@@ -9202,7 +9614,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9215,7 +9631,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1340-9067-CM25</t>
+          <t>3326-545-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9235,48 +9651,52 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>23986.66</v>
+        <v>77666.49000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3326-545-CM25</t>
+          <t>1340-9067-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9296,52 +9716,48 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.585.230-3</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>77666.49000000001</v>
+        <v>23986.66</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2981-1601-CM25</t>
+          <t>5890-187-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9389,7 +9805,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9402,7 +9822,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5890-187-CM25</t>
+          <t>2981-1601-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9450,7 +9870,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9463,7 +9887,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>29-589-CM25</t>
+          <t>796305-80-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9483,12 +9907,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -9498,33 +9922,37 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>49083.79</v>
+        <v>17662.63</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>995118-180-CM25</t>
+          <t>2974-641-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9549,43 +9977,47 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>50233.74</v>
+        <v>46279.36</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>796305-80-CM25</t>
+          <t>29-589-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9605,12 +10037,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -9620,27 +10052,31 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>17662.63</v>
+        <v>49083.79</v>
       </c>
     </row>
     <row r="150">
@@ -9694,7 +10130,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9707,7 +10147,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2974-641-CM25</t>
+          <t>995118-180-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9732,37 +10172,41 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>46279.36</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="152">
@@ -9816,7 +10260,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9877,7 +10325,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9938,7 +10390,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9999,7 +10455,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10060,7 +10520,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10121,7 +10585,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10182,7 +10650,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10243,7 +10715,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10256,7 +10732,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3311-137-CM25</t>
+          <t>3276-37-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10291,7 +10767,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10304,7 +10780,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10317,7 +10797,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3276-37-CM25</t>
+          <t>3311-137-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10352,7 +10832,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10365,7 +10845,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10378,7 +10862,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3326-610-CM25</t>
+          <t>998-290-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10403,43 +10887,47 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>Janssen S.A.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>81.198.100-1</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>66039.63</v>
+        <v>113953.77</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>998-290-CM25</t>
+          <t>3326-610-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10464,32 +10952,32 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Janssen S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>81.198.100-1</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10498,13 +10986,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>113953.77</v>
+        <v>66039.63</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1001-275-CM25</t>
+          <t>1001-280-SE25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10544,12 +11032,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>EQUIPOS Y CAMIONES SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>77.517.323-8</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -10563,13 +11051,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>146159.45</v>
+        <v>153974.09</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1001-277-CM25</t>
+          <t>1001-275-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10609,17 +11097,17 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10628,7 +11116,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>245677.7</v>
+        <v>146159.45</v>
       </c>
     </row>
     <row r="166">
@@ -10699,7 +11187,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1001-280-SE25</t>
+          <t>1001-277-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10739,17 +11227,17 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>EQUIPOS Y CAMIONES SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.517.323-8</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10758,7 +11246,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>153974.09</v>
+        <v>245677.7</v>
       </c>
     </row>
     <row r="168">
@@ -10812,7 +11300,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10873,7 +11365,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10934,7 +11430,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10947,7 +11447,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2366-4462-CM25</t>
+          <t>2585-4705-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10995,20 +11495,24 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>73486.73</v>
+        <v>21580.27</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2585-4705-CM25</t>
+          <t>2366-4461-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11048,28 +11552,32 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>21580.27</v>
+        <v>69219.13</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2366-4461-CM25</t>
+          <t>2366-4462-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11109,22 +11617,26 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>69219.13</v>
+        <v>73486.73</v>
       </c>
     </row>
     <row r="174">
@@ -11373,7 +11885,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11499,7 +12015,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11560,7 +12080,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11573,7 +12097,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1596-42-CM26</t>
+          <t>2369-128-SE25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11588,7 +12112,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11598,32 +12122,32 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11632,7 +12156,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>154730.6</v>
+        <v>389190.6</v>
       </c>
     </row>
     <row r="182">
@@ -11768,7 +12292,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>29-1421-CM26</t>
+          <t>1596-42-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11783,7 +12307,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11793,43 +12317,47 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>50773.11</v>
+        <v>154730.6</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5190-115-CM26</t>
+          <t>29-1421-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11839,12 +12367,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11854,12 +12382,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11869,28 +12397,32 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>23948.71</v>
+        <v>50773.11</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3595-140-CM26</t>
+          <t>5190-115-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11900,12 +12432,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11915,48 +12447,52 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>75622.14</v>
+        <v>23948.71</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>539119-1130-CM26</t>
+          <t>3595-140-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11966,7 +12502,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11976,43 +12512,47 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>42400.66</v>
+        <v>75622.14</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>796297-45-CM26</t>
+          <t>539119-1130-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12022,12 +12562,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -12037,43 +12577,47 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>39644.24</v>
+        <v>42400.66</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1080936-82-CM26</t>
+          <t>796297-45-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12088,7 +12632,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12098,43 +12642,47 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>60.506.012-9</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>74050.67999999999</v>
+        <v>39644.24</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>29-1644-CM26</t>
+          <t>1080936-82-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12149,7 +12697,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12159,12 +12707,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>60.506.012-9</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12174,28 +12722,32 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>57146.37</v>
+        <v>74050.67999999999</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1596-123-CM26</t>
+          <t>29-1644-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12210,37 +12762,37 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12250,13 +12802,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>36894.63</v>
+        <v>57146.37</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3595-236-CM26</t>
+          <t>1596-123-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12266,58 +12818,62 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>38997.21</v>
+        <v>36894.63</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1269-43-CM26</t>
+          <t>3595-236-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12332,53 +12888,57 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>28388.86</v>
+        <v>38997.21</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2585-483-CM26</t>
+          <t>1269-43-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12393,53 +12953,57 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr"/>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>62187.89</v>
+        <v>28388.86</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5042-25-CM26</t>
+          <t>2585-483-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12449,12 +13013,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12487,20 +13051,24 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>22670.48</v>
+        <v>62187.89</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5240-180-SE26</t>
+          <t>5042-25-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12515,7 +13083,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12525,32 +13093,32 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12559,13 +13127,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>121520.79</v>
+        <v>22670.48</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5240-169-CM26</t>
+          <t>5240-180-SE26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12580,7 +13148,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12605,28 +13173,32 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>166290.37</v>
+        <v>121520.79</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>5240-169-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12646,32 +13218,32 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12681,13 +13253,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>41321.44</v>
+        <v>166290.37</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12735,20 +13307,24 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1340.1</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1782-12-CM26</t>
+          <t>1596-186-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12763,7 +13339,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12773,32 +13349,32 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12807,13 +13383,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>654540.41</v>
+        <v>1340.1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4374-44-CM26</t>
+          <t>1782-12-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12823,12 +13399,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12838,43 +13414,47 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>25010.09</v>
+        <v>654540.41</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1596-199-CM26</t>
+          <t>4374-44-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12889,7 +13469,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12899,32 +13479,32 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -12933,13 +13513,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>113982.42</v>
+        <v>25010.09</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>3326-455-CM26</t>
+          <t>1596-199-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12959,22 +13539,22 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12987,20 +13567,24 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>29282.78</v>
+        <v>113982.42</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3326-457-CM26</t>
+          <t>3326-455-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13040,28 +13624,32 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>43132.89</v>
+        <v>29282.78</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2585-931-CM26</t>
+          <t>3326-457-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13071,58 +13659,62 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>38112.64</v>
+        <v>43132.89</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5240-192-CM26</t>
+          <t>2585-931-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13137,7 +13729,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13147,32 +13739,32 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13181,13 +13773,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>61547.18</v>
+        <v>38112.64</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>29-1907-CM26</t>
+          <t>5240-192-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13202,7 +13794,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13212,12 +13804,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13227,28 +13819,32 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr"/>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>58176.41</v>
+        <v>61547.18</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>29-1925-CM26</t>
+          <t>29-1907-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13263,7 +13859,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13296,78 +13892,147 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>74255.63</v>
+        <v>58176.41</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>29-1925-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>61.103.035-5</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>74255.63</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
           <t>1596-228-CM26</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>2239-6-LR25</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>72.227.000-2</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H210" t="inlineStr">
         <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="I210" t="inlineStr">
         <is>
           <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
+      <c r="J210" t="inlineStr">
         <is>
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="K210" t="inlineStr">
         <is>
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M209" s="2" t="n">
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
         <v>122392.49</v>
       </c>
     </row>

--- a/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
+++ b/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M210"/>
+  <dimension ref="A1:M226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1095,7 +1095,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3326-69-CM25</t>
+          <t>1067526-35-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1120,32 +1120,32 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>28911.07</v>
+        <v>70508.50999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1018-47-CM25</t>
+          <t>1067526-36-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1170,42 +1170,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>24951.73</v>
+        <v>34543.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4229-16-CM25</t>
+          <t>3326-69-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1284,13 +1284,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>20665.57</v>
+        <v>28911.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4374-1-CM25</t>
+          <t>1018-47-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,37 +1305,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>106344.99</v>
+        <v>24951.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3326-90-CM25</t>
+          <t>4374-1-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1380,27 +1380,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1414,13 +1414,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>16699.2</v>
+        <v>106344.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>796297-29-CM25</t>
+          <t>4229-16-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1445,32 +1445,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>44571.26</v>
+        <v>20665.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5240-33-CM25</t>
+          <t>3326-90-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1525,28 +1525,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>206957.36</v>
+        <v>16699.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1019-113-CM25</t>
+          <t>796297-29-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,53 +1565,57 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>25932.35</v>
+        <v>44571.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>946-1-CM25</t>
+          <t>5240-33-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1622,57 +1630,53 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>35519.88</v>
+        <v>206957.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>944-1-CM25</t>
+          <t>1019-113-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1687,12 +1691,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1707,37 +1711,33 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>35519.88</v>
+        <v>25932.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>937-2-CM25</t>
+          <t>946-1-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>35109.31</v>
+        <v>35519.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1207-1-CM25</t>
+          <t>944-1-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>35109.31</v>
+        <v>35519.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3326-130-CM25</t>
+          <t>937-2-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1877,42 +1877,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>40623.8</v>
+        <v>35109.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1080936-81-CM25</t>
+          <t>1207-1-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1942,42 +1942,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.506.012-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>22502.88</v>
+        <v>35109.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3326-141-CM25</t>
+          <t>3326-130-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>21219.65</v>
+        <v>40623.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5190-161-CM25</t>
+          <t>1080936-81-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>60.506.012-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2102,17 +2102,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>35760.18</v>
+        <v>22502.88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5240-46-CM25</t>
+          <t>3326-141-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2167,28 +2167,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>180521.63</v>
+        <v>21219.65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1044-24-CM25</t>
+          <t>5190-161-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2203,22 +2207,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2228,17 +2232,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2247,13 +2251,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>35180.58</v>
+        <v>35760.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1095-21-CM25</t>
+          <t>5240-46-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2268,57 +2272,53 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>35180.58</v>
+        <v>180521.63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3326-158-CM25</t>
+          <t>1044-24-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2338,17 +2338,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>23626.12</v>
+        <v>35180.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1095-22-CM25</t>
+          <t>3326-158-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2398,53 +2398,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SKC Transportes S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.176.602-3</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>125218.09</v>
+        <v>23626.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3326-172-CM25</t>
+          <t>1095-21-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2459,42 +2463,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2503,13 +2507,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>25298.63</v>
+        <v>35180.58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29-147-CM25</t>
+          <t>1095-22-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2524,57 +2528,53 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SKC Transportes S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.176.602-3</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>22495.04</v>
+        <v>125218.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>29-146-CM25</t>
+          <t>3326-172-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>49898.67</v>
+        <v>25298.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3326-179-CM25</t>
+          <t>29-147-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2698,13 +2698,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>20551.71</v>
+        <v>22495.04</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>539119-3510-CM25</t>
+          <t>29-146-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2729,32 +2729,32 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>31850.29</v>
+        <v>49898.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1094-3-CM25</t>
+          <t>5190-186-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2789,37 +2789,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2828,13 +2828,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>26458.93</v>
+        <v>27121.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5190-186-CM25</t>
+          <t>539119-3510-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2859,32 +2859,32 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2893,13 +2893,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>27121.28</v>
+        <v>31850.29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>557970-21-CM25</t>
+          <t>3326-179-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2919,37 +2919,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>27121.28</v>
+        <v>20551.71</v>
       </c>
     </row>
     <row r="40">
@@ -3029,7 +3029,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5240-93-CM25</t>
+          <t>557970-21-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3088,13 +3088,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>266842.13</v>
+        <v>27121.28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1096-52-CM25</t>
+          <t>1094-3-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3104,17 +3104,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3129,22 +3129,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>KOMATSU CHILE S.A.- CASA MATRIZ</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.843.130-7</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3153,13 +3153,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>370810.97</v>
+        <v>26458.93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5240-92-CM25</t>
+          <t>5240-93-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3218,13 +3218,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>25022.09</v>
+        <v>266842.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3326-201-CM25</t>
+          <t>1096-52-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3249,32 +3249,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOMATSU CHILE S.A.- CASA MATRIZ</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.843.130-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>24484.07</v>
+        <v>370810.97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3595-188-CM25</t>
+          <t>5240-92-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3314,27 +3314,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3348,13 +3348,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>82034.28</v>
+        <v>25022.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3326-209-CM25</t>
+          <t>2345-347-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3369,22 +3369,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3394,17 +3394,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3413,13 +3413,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>22716.93</v>
+        <v>27242.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3474-390-CM25</t>
+          <t>3326-201-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3459,17 +3459,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3478,13 +3478,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>35603.63</v>
+        <v>24484.07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3474-410-CM25</t>
+          <t>1063796-29-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3509,47 +3509,43 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>48335.27</v>
+        <v>10189.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3326-236-CM25</t>
+          <t>3326-209-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3559,12 +3555,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3589,17 +3585,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3608,13 +3604,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>28453.69</v>
+        <v>22716.93</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1271-23-CM25</t>
+          <t>3474-390-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3624,12 +3620,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3639,32 +3635,32 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3673,13 +3669,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>26380.6</v>
+        <v>35603.63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1268-33-CM25</t>
+          <t>3474-410-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3689,12 +3685,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3704,32 +3700,32 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3738,13 +3734,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>26093.86</v>
+        <v>48335.27</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3326-240-CM25</t>
+          <t>3326-236-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3759,7 +3755,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3803,13 +3799,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>28534</v>
+        <v>28453.69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5240-112-CM25</t>
+          <t>1271-23-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3824,7 +3820,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3834,32 +3830,32 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3868,13 +3864,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>298849.7</v>
+        <v>26380.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>976-171-CM25</t>
+          <t>1268-33-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3889,7 +3885,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3909,22 +3905,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3933,13 +3929,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>27383.7</v>
+        <v>26093.86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>975-120-CM25</t>
+          <t>5240-112-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3954,22 +3950,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3979,17 +3975,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3998,13 +3994,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>210423.71</v>
+        <v>298849.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5240-98-CM25</t>
+          <t>3326-240-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4019,7 +4015,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4044,17 +4040,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4063,13 +4059,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>60218.1</v>
+        <v>28534</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3326-259-CM25</t>
+          <t>976-171-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4084,7 +4080,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4094,12 +4090,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4109,12 +4105,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4128,13 +4124,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>19259.23</v>
+        <v>27383.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3326-263-CM25</t>
+          <t>975-120-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4149,7 +4145,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4159,12 +4155,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4174,17 +4170,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4193,13 +4189,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>49998.52</v>
+        <v>210423.71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4374-58-CM25</t>
+          <t>5240-98-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4214,7 +4210,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4224,32 +4220,32 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4258,13 +4254,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>474892.33</v>
+        <v>60218.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3326-277-CM25</t>
+          <t>3326-259-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4274,12 +4270,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4304,12 +4300,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4323,13 +4319,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>33736.15</v>
+        <v>19259.23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1596-160-CM25</t>
+          <t>3326-263-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4339,42 +4335,42 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4388,13 +4384,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>213461.61</v>
+        <v>49998.52</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5240-165-CM25</t>
+          <t>4374-58-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4404,12 +4400,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4419,43 +4415,47 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>94924.60000000001</v>
+        <v>474892.33</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3595-281-CM25</t>
+          <t>1596-160-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4480,32 +4480,32 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4514,13 +4514,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>35676.71</v>
+        <v>213461.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3326-296-CM25</t>
+          <t>3326-277-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4579,13 +4579,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>28411.88</v>
+        <v>33736.15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1044-49-CM25</t>
+          <t>2345-466-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>DERCOMAQ SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.545.450-0</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>66160.02</v>
+        <v>55349.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3326-298-CM25</t>
+          <t>5240-165-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4690,32 +4690,28 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>27750.29</v>
+        <v>94924.60000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4374-63-CM25</t>
+          <t>3326-296-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4730,7 +4726,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4740,32 +4736,32 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4774,13 +4770,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>75561.98</v>
+        <v>28411.88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3595-308-CM25</t>
+          <t>3326-298-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4795,7 +4791,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4805,32 +4801,32 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4839,13 +4835,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>44302.74</v>
+        <v>27750.29</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2369-37-CM25</t>
+          <t>1044-49-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4860,42 +4856,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4904,13 +4900,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>364772.75</v>
+        <v>66160.02</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3326-318-CM25</t>
+          <t>4374-63-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4925,7 +4921,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4935,32 +4931,32 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4969,13 +4965,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>20521.92</v>
+        <v>75561.98</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3595-341-CM25</t>
+          <t>2369-37-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4985,12 +4981,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5000,32 +4996,32 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>KOMATSU CHILE S.A.- CASA MATRIZ</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.843.130-7</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5034,13 +5030,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>356715.75</v>
+        <v>364772.75</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3326-340-CM25</t>
+          <t>3326-318-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5050,12 +5046,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5080,17 +5076,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5099,13 +5095,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>18377.44</v>
+        <v>20521.92</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>609-342-CM25</t>
+          <t>4988-33-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5115,12 +5111,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5130,47 +5126,43 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Cecor S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.010.151-6</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>40569.75</v>
+        <v>43838.88</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3326-357-CM25</t>
+          <t>3326-340-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5185,7 +5177,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5210,17 +5202,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5229,13 +5221,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>27954.44</v>
+        <v>18377.44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1051425-97-CM25</t>
+          <t>4988-39-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5250,7 +5242,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5260,43 +5252,47 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>35723.62</v>
+        <v>230449.24</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1455288-29-CM25</t>
+          <t>3326-357-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5311,7 +5307,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5321,12 +5317,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5336,17 +5332,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5355,13 +5351,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>23929.56</v>
+        <v>27954.44</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2974-514-CM25</t>
+          <t>1051425-97-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5376,7 +5372,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5386,47 +5382,43 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>24152.48</v>
+        <v>35723.62</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3326-374-CM25</t>
+          <t>2974-514-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5451,12 +5443,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5466,17 +5458,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5485,13 +5477,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>27881.27</v>
+        <v>24152.48</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1596-208-CM25</t>
+          <t>3326-374-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5506,7 +5498,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5516,17 +5508,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5550,13 +5542,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>133329.6</v>
+        <v>27881.27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>609-329-CM25</t>
+          <t>1455288-29-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5571,7 +5563,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5581,12 +5573,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5596,17 +5588,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5615,13 +5607,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>404994.09</v>
+        <v>23929.56</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>609-337-CM25</t>
+          <t>1596-208-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5636,7 +5628,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5646,32 +5638,32 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5680,7 +5672,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>135478.99</v>
+        <v>133329.6</v>
       </c>
     </row>
     <row r="82">
@@ -6206,7 +6198,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>976-301-CM25</t>
+          <t>1020-327-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6226,7 +6218,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6246,28 +6238,32 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>33706.1</v>
+        <v>80696.36</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1020-327-CM25</t>
+          <t>976-301-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6287,7 +6283,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6307,26 +6303,22 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>80696.36</v>
+        <v>33706.1</v>
       </c>
     </row>
     <row r="92">
@@ -6397,7 +6389,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>998-218-CM25</t>
+          <t>979-1634-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6432,17 +6424,17 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6456,13 +6448,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>50934.76</v>
+        <v>48009.23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>979-1634-CM25</t>
+          <t>998-218-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6497,17 +6489,17 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6521,7 +6513,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>48009.23</v>
+        <v>50934.76</v>
       </c>
     </row>
     <row r="95">
@@ -6970,7 +6962,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3326-495-CM25</t>
+          <t>3326-489-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7010,17 +7002,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7029,13 +7021,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>44016.94</v>
+        <v>20419.51</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3326-489-CM25</t>
+          <t>3326-495-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7075,17 +7067,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7094,7 +7086,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>20419.51</v>
+        <v>44016.94</v>
       </c>
     </row>
     <row r="104">
@@ -7356,7 +7348,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5190-362-CM25</t>
+          <t>1080157-124-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7381,32 +7373,32 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7415,13 +7407,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>29503.1</v>
+        <v>49470.76</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1148-105-CM25</t>
+          <t>5190-362-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7441,37 +7433,37 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7480,13 +7472,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>26801.81</v>
+        <v>29503.1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1080157-124-CM25</t>
+          <t>1148-105-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7506,37 +7498,37 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7545,7 +7537,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>49470.76</v>
+        <v>26801.81</v>
       </c>
     </row>
     <row r="111">
@@ -7746,7 +7738,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3326-535-CM25</t>
+          <t>4180-159-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7771,7 +7763,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7781,22 +7773,22 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7805,7 +7797,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>30610.16</v>
+        <v>23337.98</v>
       </c>
     </row>
     <row r="115">
@@ -7876,7 +7868,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4180-159-CM25</t>
+          <t>3326-535-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7901,7 +7893,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7911,22 +7903,22 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7935,7 +7927,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>23337.98</v>
+        <v>30610.16</v>
       </c>
     </row>
     <row r="117">
@@ -8006,7 +7998,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4230-160-CM25</t>
+          <t>1095-90-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8026,37 +8018,37 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8065,13 +8057,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>25413.54</v>
+        <v>39510.7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1095-90-CM25</t>
+          <t>4230-160-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8091,37 +8083,37 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8130,7 +8122,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>39510.7</v>
+        <v>25413.54</v>
       </c>
     </row>
     <row r="120">
@@ -8331,7 +8323,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1340-9046-CM25</t>
+          <t>1340-9047-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8371,12 +8363,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8390,13 +8382,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>142633.04</v>
+        <v>141384.98</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1340-9047-CM25</t>
+          <t>1340-9046-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8436,12 +8428,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8455,7 +8447,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>141384.98</v>
+        <v>142633.04</v>
       </c>
     </row>
     <row r="125">
@@ -8526,7 +8518,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3323-118-CM25</t>
+          <t>3453-590-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8591,7 +8583,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3453-590-CM25</t>
+          <t>3323-118-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8656,7 +8648,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4077-106-CM25</t>
+          <t>3474-819-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8681,7 +8673,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -8691,22 +8683,22 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8715,13 +8707,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>48894.85</v>
+        <v>28864.67</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3474-818-CM25</t>
+          <t>4077-106-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8746,7 +8738,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8756,22 +8748,22 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8780,13 +8772,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>28864.67</v>
+        <v>48894.85</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3474-819-CM25</t>
+          <t>3474-818-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8916,7 +8908,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4232-160-CM25</t>
+          <t>3326-552-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8941,7 +8933,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8951,7 +8943,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8975,13 +8967,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>25371.37</v>
+        <v>242574.63</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3326-552-CM25</t>
+          <t>4232-160-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9006,7 +8998,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9016,7 +9008,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9040,7 +9032,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>242574.63</v>
+        <v>25371.37</v>
       </c>
     </row>
     <row r="134">
@@ -9176,7 +9168,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3434-120-CM25</t>
+          <t>539119-10421-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9201,7 +9193,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -9211,22 +9203,22 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9235,13 +9227,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>28966.32</v>
+        <v>17279.98</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4230-173-CM25</t>
+          <t>3434-120-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9266,7 +9258,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9276,22 +9268,22 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9300,13 +9292,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>24888.81</v>
+        <v>28966.32</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>539119-10421-CM25</t>
+          <t>4230-173-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9331,7 +9323,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -9341,22 +9333,22 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9365,7 +9357,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>17279.98</v>
+        <v>24888.81</v>
       </c>
     </row>
     <row r="139">
@@ -9436,7 +9428,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4232-159-CM25</t>
+          <t>1080164-33-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9461,7 +9453,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -9471,7 +9463,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9501,7 +9493,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1080164-33-CM25</t>
+          <t>4232-159-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9526,7 +9518,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -9536,7 +9528,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9757,7 +9749,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5890-187-CM25</t>
+          <t>2981-1601-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9822,7 +9814,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2981-1601-CM25</t>
+          <t>5890-187-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9887,7 +9879,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>796305-80-CM25</t>
+          <t>2974-641-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9907,7 +9899,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9922,7 +9914,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9946,13 +9938,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>17662.63</v>
+        <v>46279.36</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2974-641-CM25</t>
+          <t>995118-180-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9977,32 +9969,32 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -10011,13 +10003,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>46279.36</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>29-589-CM25</t>
+          <t>3326-597-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10042,12 +10034,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10057,17 +10049,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10076,13 +10068,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>49083.79</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3326-597-CM25</t>
+          <t>29-589-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10107,12 +10099,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10122,17 +10114,17 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -10141,13 +10133,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>50233.74</v>
+        <v>49083.79</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>995118-180-CM25</t>
+          <t>796305-80-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10167,37 +10159,37 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -10206,7 +10198,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>50233.74</v>
+        <v>17662.63</v>
       </c>
     </row>
     <row r="152">
@@ -11057,7 +11049,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1001-275-CM25</t>
+          <t>1001-279-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11097,12 +11089,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11116,13 +11108,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>146159.45</v>
+        <v>49842.18</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1001-279-CM25</t>
+          <t>1001-277-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11162,17 +11154,17 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -11181,13 +11173,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>49842.18</v>
+        <v>245677.7</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1001-277-CM25</t>
+          <t>1001-275-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11227,17 +11219,17 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -11246,7 +11238,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>245677.7</v>
+        <v>146159.45</v>
       </c>
     </row>
     <row r="168">
@@ -11512,7 +11504,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2366-4461-CM25</t>
+          <t>2366-4462-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11552,17 +11544,17 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11571,13 +11563,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>69219.13</v>
+        <v>73486.73</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2366-4462-CM25</t>
+          <t>2366-4461-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11617,17 +11609,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11636,13 +11628,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>73486.73</v>
+        <v>69219.13</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>979-2135-CM25</t>
+          <t>5240-296-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11662,17 +11654,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11682,12 +11674,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -11701,13 +11693,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>582696.4300000001</v>
+        <v>291974.24</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5240-296-CM25</t>
+          <t>979-2135-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11727,17 +11719,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11747,12 +11739,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11766,7 +11758,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>291974.24</v>
+        <v>582696.4300000001</v>
       </c>
     </row>
     <row r="176">
@@ -11967,7 +11959,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3326-39-CM26</t>
+          <t>2560-127-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11977,27 +11969,27 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12007,17 +11999,17 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -12026,13 +12018,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>48077.59</v>
+        <v>95375.27</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3326-47-CM26</t>
+          <t>2560-141-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12047,22 +12039,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12072,12 +12064,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -12091,13 +12083,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>37727.35</v>
+        <v>124455.56</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2369-128-SE25</t>
+          <t>3326-39-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12107,12 +12099,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -12122,32 +12114,32 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -12156,13 +12148,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>389190.6</v>
+        <v>48077.59</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2369-117-CM25</t>
+          <t>3326-47-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12172,47 +12164,47 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -12221,13 +12213,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>218722.92</v>
+        <v>37727.35</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1596-40-CM26</t>
+          <t>2369-128-SE25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12242,7 +12234,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -12252,32 +12244,32 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -12286,7 +12278,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>123574.14</v>
+        <v>389190.6</v>
       </c>
     </row>
     <row r="184">
@@ -12357,7 +12349,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>29-1421-CM26</t>
+          <t>1596-40-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12372,7 +12364,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -12382,32 +12374,32 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -12416,13 +12408,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>50773.11</v>
+        <v>123574.14</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5190-115-CM26</t>
+          <t>2369-117-CM25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12432,47 +12424,47 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -12481,13 +12473,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>23948.71</v>
+        <v>218722.92</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3595-140-CM26</t>
+          <t>29-1421-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12497,12 +12489,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12512,32 +12504,32 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12546,63 +12538,63 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>75622.14</v>
+        <v>50773.11</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>539119-1130-CM26</t>
+          <t>4988-6-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Guillermo Morales Ltda</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.564.810-0</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12611,28 +12603,28 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>42400.66</v>
+        <v>104460.72</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>796297-45-CM26</t>
+          <t>5190-115-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12642,17 +12634,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12676,13 +12668,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>39644.24</v>
+        <v>23948.71</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1080936-82-CM26</t>
+          <t>539119-1130-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12692,12 +12684,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12707,12 +12699,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>60.506.012-9</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12722,17 +12714,17 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12741,13 +12733,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>74050.67999999999</v>
+        <v>42400.66</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>29-1644-CM26</t>
+          <t>796297-45-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12762,7 +12754,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12772,7 +12764,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -12782,33 +12774,37 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>57146.37</v>
+        <v>39644.24</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1596-123-CM26</t>
+          <t>1080936-82-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12823,27 +12819,27 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.506.012-9</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12867,13 +12863,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>36894.63</v>
+        <v>74050.67999999999</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3595-236-CM26</t>
+          <t>29-1644-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12883,12 +12879,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12898,47 +12894,43 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>38997.21</v>
+        <v>57146.37</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1269-43-CM26</t>
+          <t>1596-123-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12948,12 +12940,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12963,32 +12955,32 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12997,13 +12989,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>28388.86</v>
+        <v>36894.63</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2585-483-CM26</t>
+          <t>1269-43-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13018,42 +13010,42 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -13062,13 +13054,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>62187.89</v>
+        <v>28388.86</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5042-25-CM26</t>
+          <t>2585-483-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13078,12 +13070,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -13127,13 +13119,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>22670.48</v>
+        <v>62187.89</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5240-180-SE26</t>
+          <t>2345-261-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13143,27 +13135,27 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13173,12 +13165,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13192,13 +13184,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>121520.79</v>
+        <v>601.49</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5240-169-CM26</t>
+          <t>2345-260-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13208,27 +13200,27 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13238,28 +13230,32 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>166290.37</v>
+        <v>27811.39</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>5042-25-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13274,42 +13270,42 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -13318,13 +13314,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>41321.44</v>
+        <v>22670.48</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>5240-180-SE26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13339,42 +13335,42 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13383,13 +13379,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1340.1</v>
+        <v>121520.79</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1782-12-CM26</t>
+          <t>5240-169-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13404,57 +13400,53 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>654540.41</v>
+        <v>166290.37</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4374-44-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13464,12 +13456,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -13479,32 +13471,32 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13513,13 +13505,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>25010.09</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1596-199-CM26</t>
+          <t>1596-186-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13529,12 +13521,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -13559,17 +13551,17 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -13578,13 +13570,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>113982.42</v>
+        <v>1340.1</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3326-455-CM26</t>
+          <t>1782-12-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13594,42 +13586,42 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -13643,13 +13635,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>29282.78</v>
+        <v>654540.41</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3326-457-CM26</t>
+          <t>2416-201-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13664,42 +13656,42 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13708,13 +13700,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>43132.89</v>
+        <v>42840</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2585-931-CM26</t>
+          <t>4374-44-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13724,12 +13716,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13739,32 +13731,32 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13773,13 +13765,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>38112.64</v>
+        <v>25010.09</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5240-192-CM26</t>
+          <t>3326-455-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13789,17 +13781,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -13819,17 +13811,17 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13838,13 +13830,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>61547.18</v>
+        <v>29282.78</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>29-1907-CM26</t>
+          <t>1596-199-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13854,12 +13846,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13869,17 +13861,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13903,13 +13895,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>58176.41</v>
+        <v>113982.42</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>29-1925-CM26</t>
+          <t>3326-457-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13919,27 +13911,27 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13949,12 +13941,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -13968,72 +13960,1108 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>74255.63</v>
+        <v>43132.89</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
+          <t>2585-931-CM26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>38112.64</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>5240-192-CM26</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>61.938.500-4</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="n">
+        <v>61547.18</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>29-1907-CM26</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>61.103.035-5</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="n">
+        <v>58176.41</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2345-480-CM26</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="n">
+        <v>61963.39</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>625-339-CM26</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>61.103.035-5</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="n">
+        <v>37372.39</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>29-1925-CM26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>61.103.035-5</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>74255.63</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
           <t>1596-228-CM26</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>2239-6-LR25</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E216" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>72.227.000-2</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G216" t="inlineStr">
         <is>
           <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
+      <c r="H216" t="inlineStr">
         <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I216" t="inlineStr">
         <is>
           <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr">
+      <c r="J216" t="inlineStr">
         <is>
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="K216" t="inlineStr">
         <is>
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M210" s="2" t="n">
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="n">
         <v>122392.49</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>4988-90-CM26</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>360459.05</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2345-541-CM26</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>FINNING CHILE S A</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>91.489.000-4</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="n">
+        <v>313878.96</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2345-544-CM26</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="n">
+        <v>87954.36</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1596-280-CM26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="n">
+        <v>68043.28999999999</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1596-281-CM26</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="n">
+        <v>882.47</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2369-149-CM26</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>43706.87</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1079563-449-CM26</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>61.978.680-7</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>34940.12</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>4988-116-CM26</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>EPYSA BUSES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>77.824.870-0</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="n">
+        <v>544269.13</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>3453-497-CM26</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="n">
+        <v>2969.49</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>3453-496-CM26</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="n">
+        <v>70518</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
+++ b/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
@@ -12044,7 +12044,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">

--- a/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
+++ b/docs/oc-top-organismos/adquisicion-de-vehiculos-y-maquinaria.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M226"/>
+  <dimension ref="A1:M227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5418,7 +5418,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2974-514-CM25</t>
+          <t>1455288-29-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>24152.48</v>
+        <v>23929.56</v>
       </c>
     </row>
     <row r="79">
@@ -5548,7 +5548,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1455288-29-CM25</t>
+          <t>2974-514-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>23929.56</v>
+        <v>24152.48</v>
       </c>
     </row>
     <row r="81">
@@ -5743,7 +5743,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2585-4029-CM25</t>
+          <t>1596-206-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5768,32 +5768,32 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5802,13 +5802,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>34510.01</v>
+        <v>149130.92</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1596-206-CM25</t>
+          <t>2585-4029-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>149130.92</v>
+        <v>34510.01</v>
       </c>
     </row>
     <row r="85">
@@ -6198,7 +6198,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1020-327-CM25</t>
+          <t>976-301-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6238,32 +6238,28 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>80696.36</v>
+        <v>33706.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>976-301-CM25</t>
+          <t>1020-327-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6283,7 +6279,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6303,22 +6299,26 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>33706.1</v>
+        <v>80696.36</v>
       </c>
     </row>
     <row r="92">
@@ -6389,7 +6389,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>979-1634-CM25</t>
+          <t>998-218-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6424,17 +6424,17 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6448,13 +6448,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>48009.23</v>
+        <v>50934.76</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>998-218-CM25</t>
+          <t>979-1634-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6489,17 +6489,17 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>50934.76</v>
+        <v>48009.23</v>
       </c>
     </row>
     <row r="95">
@@ -7348,7 +7348,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1080157-124-CM25</t>
+          <t>5190-362-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7373,32 +7373,32 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7407,13 +7407,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>49470.76</v>
+        <v>29503.1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5190-362-CM25</t>
+          <t>1080157-124-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>29503.1</v>
+        <v>49470.76</v>
       </c>
     </row>
     <row r="110">
@@ -8323,7 +8323,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1340-9047-CM25</t>
+          <t>1340-9046-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8382,13 +8382,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>141384.98</v>
+        <v>142633.04</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1340-9046-CM25</t>
+          <t>1340-9047-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>142633.04</v>
+        <v>141384.98</v>
       </c>
     </row>
     <row r="125">
@@ -13385,7 +13385,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5240-169-CM26</t>
+          <t>1596-186-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13405,48 +13405,52 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>166290.37</v>
+        <v>1340.1</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>5240-169-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13466,52 +13470,48 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>41321.44</v>
+        <v>166290.37</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1340.1</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="204">
@@ -14937,7 +14937,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3453-497-CM26</t>
+          <t>3453-496-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14996,13 +14996,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2969.49</v>
+        <v>70518</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3453-496-CM26</t>
+          <t>3453-497-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15061,7 +15061,68 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>70518</v>
+        <v>2969.49</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2345-557-CM26</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>HVCCSA</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>76.758.790-2</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="n">
+        <v>45461.19</v>
       </c>
     </row>
   </sheetData>
